--- a/DateBase/orders/Dang Nguyen48_2026-4-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-12.xlsx
@@ -1452,6 +1452,9 @@
       <c r="C121" t="str">
         <v>85_摩洛哥_undefined_Gerbera L._10stems</v>
       </c>
+      <c r="F121" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1510,7 +1513,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0535555510105155155105510151015105555510551055105555510101010303030201055551058887107.5188101010550105555101066105555107835205108105510105555101010555301010510510551510150</v>
+        <v>0535555510105155155105510151015105555510551055105555510101010303030201055551058887107.51881010105501055551010661055551078352051081055101055551010105553010105105105515101510</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L127"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1456,9 +1456,60 @@
         <v>10</v>
       </c>
     </row>
+    <row r="122">
+      <c r="C122" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F122" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>5</v>
+      </c>
+      <c r="C123" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F123" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="C124" t="str">
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F124" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="C125" t="str">
+        <v>632_吸色康乃馨紫_tinted purple_undefined_20stems</v>
+      </c>
+      <c r="F125" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="C126" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F126" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F127" t="str">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L127"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1513,7 +1564,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0535555510105155155105510151015105555510551055105555510101010303030201055551058887107.51881010105501055551010661055551078352051081055101055551010105553010105105105515101510</v>
+        <v>0535555510105155155105510151015105555510551055105555510101010303030201055551058887107.518810101055010555510106610555510783520510810551010555510101055530101051051055151015103555107</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-4-12.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-4-12.xlsx
@@ -1566,6 +1566,9 @@
       <c r="G2" t="str">
         <v>0535555510105155155105510151015105555510551055105555510101010303030201055551058887107.518810101055010555510106610555510783520510810551010555510101055530101051051055151015103555107</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
